--- a/exports/invoice.xlsx
+++ b/exports/invoice.xlsx
@@ -417,14 +417,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="57" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,10 +450,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>invoice_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>vendor_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>customer_name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tax_amount</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total_amount</t>
         </is>
@@ -457,7 +487,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>invoice1.pdf</t>
+          <t>1_BAHRA-CABLES-60129398.png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,17 +497,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INV001</t>
+          <t>60129398</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1000</v>
-      </c>
+          <t>02.01.2019</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bahra Advanced Cable Manufacture Co Lid</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The Civil Works Joint Venture Of Saudi Arabian Bechtel</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/invoice.xlsx
+++ b/exports/invoice.xlsx
@@ -417,19 +417,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="57" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,84 +441,54 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>invoice_number</t>
+          <t>credit_note_number</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>invoice_date</t>
+          <t>vendor_name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>vendor_name</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>subtotal</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tax_amount</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>total_amount</t>
+          <t>amount</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1_BAHRA-CABLES-60129398.png</t>
+          <t>1_CCS-CONSTRUCTION-COMPUTER-11341.png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>invoice</t>
+          <t>credit_note</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>60129398</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>02.01.2019</t>
+          <t>Construction Computer Software (Gulf LLC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bahra Advanced Cable Manufacture Co Lid</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>The Civil Works Joint Venture Of Saudi Arabian Bechtel</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>03 March 2019</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>8600</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/invoice.xlsx
+++ b/exports/invoice.xlsx
@@ -417,15 +417,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,53 +445,89 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>credit_note_number</t>
+          <t>invoice_number</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>invoice_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>vendor_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>customer_name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tax_amount</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_amount</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1_CCS-CONSTRUCTION-COMPUTER-11341.png</t>
+          <t>1_BAHRI-BOLLORE-JED301286.png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>credit_note</t>
+          <t>invoice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>JED301286</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Construction Computer Software (Gulf LLC</t>
+          <t>02/08/2018</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>03 March 2019</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>8600</v>
+          <t>Bahri Bollore Logistics</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>RIYADH METRO PROJECT CIVIL WORKS JOINT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>7589.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>210</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7799.75</v>
       </c>
     </row>
   </sheetData>

--- a/exports/invoice.xlsx
+++ b/exports/invoice.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="41" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -445,12 +445,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>invoice_number</t>
+          <t>document_number</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>invoice_date</t>
+          <t>document_date</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>invoice</t>
+          <t>tax_document</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bahri Bollore Logistics</t>
+          <t>Bahri Bolloré Logistics</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -520,14 +520,20 @@
           <t>SAR</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>7589.75</v>
-      </c>
-      <c r="I2" t="n">
-        <v>210</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7799.75</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7,589.75</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>210.00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7,799.75</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/exports/invoice.xlsx
+++ b/exports/invoice.xlsx
@@ -417,19 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="41" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,46 +435,6 @@
           <t>document_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>document_number</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>document_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>vendor_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>subtotal</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tax_amount</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,47 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tax_document</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JED301286</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>02/08/2018</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Bahri Bolloré Logistics</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>RIYADH METRO PROJECT CIVIL WORKS JOINT</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>7,589.75</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>7,799.75</t>
+          <t>other_financial_document</t>
         </is>
       </c>
     </row>

--- a/exports/invoice.xlsx
+++ b/exports/invoice.xlsx
@@ -417,11 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -435,16 +446,116 @@
           <t>document_type</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>document_number</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>document_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>vendor_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>customer_name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tax_amount</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>maturity_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>terms_version</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>terms_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1_BAHRI-BOLLORE-JED301286.png</t>
+          <t>4_JY2020-07-JV000738.png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>other_financial_document</t>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>200024783</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Socemco industriol Co.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>C.W.J.V-s</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1501.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>75.08</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1576.575</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>29/04/2020</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>01/03/2020</t>
         </is>
       </c>
     </row>
